--- a/Студент/ошибки (2).xlsx
+++ b/Студент/ошибки (2).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v.remnev\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\uni-eng.ru\unit\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М300\Проект\Студент\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A256DD5-DBD1-4DE5-A34B-A32018CF7FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
   <si>
     <t>РЭ</t>
   </si>
@@ -231,12 +235,18 @@
   </si>
   <si>
     <t xml:space="preserve">2.27.3.2 и 2.27.3.3 </t>
+  </si>
+  <si>
+    <t>БУ</t>
+  </si>
+  <si>
+    <t>Расчет уставок ДТЗ указать что ток сраб загрубления не может быть меньше начального тока сраб и коэффициент торможения 2 участка не может быть больше кт первого участка</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -552,8 +562,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -908,6 +918,14 @@
         <v>11</v>
       </c>
     </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Студент/ошибки (2).xlsx
+++ b/Студент/ошибки (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\uni-eng.ru\unit\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М300\Проект\Студент\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A256DD5-DBD1-4DE5-A34B-A32018CF7FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085FF892-82A7-4DDC-AE92-16D093A748B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="72">
   <si>
     <t>РЭ</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Расчет уставок ДТЗ указать что ток сраб загрубления не может быть меньше начального тока сраб и коэффициент торможения 2 участка не может быть больше кт первого участка</t>
+  </si>
+  <si>
+    <t>Изменить МГН в токах УРОВ на СКЗ</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -926,6 +929,11 @@
         <v>70</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
